--- a/data/trans_dic/P16A10-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P16A10-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicamentos para el corazón en las dos últimas semanas</t>
+          <t>Población que ha consumido medicamentos para el corazón en las dos últimas semanas (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,86</t>
+          <t>0,0; 0,84</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,19</t>
+          <t>0,0; 1,07</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,11</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,2</t>
+          <t>0,0; 0,95</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,15</t>
+          <t>0,0; 1,32</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,26</t>
+          <t>0,0; 1,1</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,59</t>
+          <t>0,0; 4,35</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,56</t>
+          <t>0,0; 0,67</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,79</t>
+          <t>0,0; 0,77</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,61</t>
+          <t>0,0; 0,74</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,93</t>
+          <t>0,0; 1,85</t>
         </is>
       </c>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,69</t>
+          <t>0,0; 0,58</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -867,52 +867,52 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,45</t>
+          <t>0,0; 1,59</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,63</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,99</t>
+          <t>0,0; 0,97</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,83</t>
+          <t>0,0; 0,71</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,35; 2,21</t>
+          <t>0,35; 2,09</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,74</t>
+          <t>0,0; 1,89</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,57</t>
+          <t>0,06; 0,61</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,98</t>
+          <t>0,14; 1,05</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,33; 1,42</t>
+          <t>0,34; 1,41</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,95</t>
+          <t>0,0; 0,9</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,57</t>
+          <t>0,28; 1,73</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,56</t>
+          <t>0,28; 1,63</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,01</t>
+          <t>0,0; 1,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,19; 2,0</t>
+          <t>0,19; 2,03</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,45; 2,33</t>
+          <t>0,49; 2,35</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,61</t>
+          <t>0,7; 2,67</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,72</t>
+          <t>0,29; 1,74</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,5</t>
+          <t>0,27; 1,51</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,51; 1,66</t>
+          <t>0,48; 1,6</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,59; 1,76</t>
+          <t>0,64; 1,85</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,14</t>
+          <t>0,28; 1,07</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,32</t>
+          <t>0,3; 1,34</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,35; 4,58</t>
+          <t>1,42; 4,43</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,16; 3,91</t>
+          <t>1,08; 3,75</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,8; 4,65</t>
+          <t>1,82; 4,65</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,18; 4,68</t>
+          <t>1,23; 4,78</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,08; 5,35</t>
+          <t>2,0; 5,16</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,53; 2,49</t>
+          <t>0,53; 2,47</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,28; 3,73</t>
+          <t>1,29; 3,66</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,88; 2,3</t>
+          <t>0,84; 2,25</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,97; 4,24</t>
+          <t>2,02; 4,14</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,05; 2,7</t>
+          <t>1,1; 2,71</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,81; 3,7</t>
+          <t>1,8; 3,69</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,27; 3,12</t>
+          <t>1,29; 3,25</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,14; 14,59</t>
+          <t>8,29; 14,87</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,06; 11,11</t>
+          <t>6,16; 11,08</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,83; 13,85</t>
+          <t>7,93; 14,15</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,52; 9,73</t>
+          <t>5,52; 9,83</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,18; 9,18</t>
+          <t>4,07; 8,83</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,19; 8,72</t>
+          <t>4,11; 8,38</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,54; 4,72</t>
+          <t>1,56; 4,74</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,22; 5,86</t>
+          <t>3,28; 5,97</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,76; 10,59</t>
+          <t>6,91; 10,84</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5,68; 9,04</t>
+          <t>5,51; 9,08</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5,08; 8,56</t>
+          <t>5,02; 8,47</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,76; 7,26</t>
+          <t>4,83; 7,32</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>13,65; 22,14</t>
+          <t>13,64; 22,07</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>11,21; 19,66</t>
+          <t>11,48; 19,89</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15,5; 24,52</t>
+          <t>16,16; 24,66</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10,46; 15,79</t>
+          <t>10,46; 15,86</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>11,78; 19,13</t>
+          <t>11,64; 19,24</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7,63; 14,25</t>
+          <t>7,68; 14,32</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10,45; 17,88</t>
+          <t>10,06; 17,35</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,16; 8,59</t>
+          <t>2,26; 8,81</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>13,67; 19,26</t>
+          <t>13,52; 19,03</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>10,22; 15,4</t>
+          <t>10,39; 15,53</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>13,82; 19,4</t>
+          <t>13,83; 19,63</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>4,4; 10,87</t>
+          <t>4,23; 11,05</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>24,07; 36,58</t>
+          <t>24,04; 37,03</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>24,3; 36,56</t>
+          <t>23,81; 36,7</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>19,19; 28,77</t>
+          <t>19,25; 29,07</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>20,0; 27,92</t>
+          <t>20,02; 28,59</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>17,76; 26,97</t>
+          <t>17,79; 27,46</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,25; 26,98</t>
+          <t>18,3; 26,96</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,24; 29,6</t>
+          <t>19,79; 29,64</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>21,51; 27,37</t>
+          <t>21,5; 27,35</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>21,98; 29,45</t>
+          <t>22,26; 29,3</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>21,95; 29,13</t>
+          <t>21,9; 29,0</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>20,95; 28,25</t>
+          <t>20,79; 27,91</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>21,84; 26,44</t>
+          <t>21,69; 26,59</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,62; 6,27</t>
+          <t>4,69; 6,19</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4,48; 6,07</t>
+          <t>4,54; 6,18</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5,11; 6,78</t>
+          <t>5,14; 6,79</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4,1; 6,18</t>
+          <t>3,92; 6,19</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,57; 6,04</t>
+          <t>4,57; 6,15</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,08; 5,55</t>
+          <t>4,13; 5,62</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,62; 6,18</t>
+          <t>4,62; 6,28</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>3,94; 5,53</t>
+          <t>4,0; 5,58</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4,8; 5,88</t>
+          <t>4,84; 5,92</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4,51; 5,55</t>
+          <t>4,48; 5,57</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5,09; 6,27</t>
+          <t>5,15; 6,26</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>4,46; 5,71</t>
+          <t>4,5; 5,74</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicamentos para el corazón en las dos últimas semanas</t>
+          <t>Población que ha consumido medicamentos para el corazón en las dos últimas semanas (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4262</t>
+          <t>0; 4164</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 5384</t>
+          <t>0; 4829</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 2044</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 4435</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 5627</t>
+          <t>0; 4459</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 4942</t>
+          <t>0; 5660</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 5002</t>
+          <t>0; 4339</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 14369</t>
+          <t>0; 13620</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 5362</t>
+          <t>0; 6422</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 6960</t>
+          <t>0; 6833</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 5007</t>
+          <t>0; 6028</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 13749</t>
+          <t>0; 13197</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 5077</t>
+          <t>0; 4229</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1032; 11406</t>
+          <t>1030; 11374</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 8583</t>
+          <t>0; 9405</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 2683</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 6203</t>
+          <t>0; 6039</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 5044</t>
+          <t>0; 4344</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1968; 12458</t>
+          <t>1976; 11754</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 8881</t>
+          <t>0; 9680</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>864; 7764</t>
+          <t>869; 8255</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1041; 12745</t>
+          <t>1870; 13573</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3784; 16347</t>
+          <t>3884; 16310</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0; 8861</t>
+          <t>0; 8392</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1825; 10033</t>
+          <t>1814; 11015</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1892; 10576</t>
+          <t>1927; 11078</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 6766</t>
+          <t>0; 6678</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1039; 10729</t>
+          <t>1033; 10876</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3116; 16059</t>
+          <t>3371; 16202</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4842; 18492</t>
+          <t>4939; 18959</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1953; 11353</t>
+          <t>1932; 11479</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1462; 8147</t>
+          <t>1453; 8190</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>6777; 22082</t>
+          <t>6410; 21182</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8189; 24396</t>
+          <t>8893; 25694</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3767; 15110</t>
+          <t>3717; 14284</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3294; 14227</t>
+          <t>3203; 14491</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7020; 23798</t>
+          <t>7352; 22980</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7116; 24033</t>
+          <t>6611; 23018</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>11605; 30027</t>
+          <t>11735; 30021</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10437; 41585</t>
+          <t>10934; 42456</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>10706; 27596</t>
+          <t>10295; 26581</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3283; 15266</t>
+          <t>3230; 15161</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8313; 24238</t>
+          <t>8345; 23733</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6238; 16382</t>
+          <t>5991; 16073</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>20371; 43884</t>
+          <t>20926; 42851</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>12917; 33168</t>
+          <t>13499; 33311</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>23436; 47924</t>
+          <t>23369; 47818</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>20322; 49930</t>
+          <t>20627; 51951</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>31472; 56433</t>
+          <t>32053; 57520</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>25941; 47576</t>
+          <t>26395; 47464</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>37435; 66205</t>
+          <t>37880; 67648</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>30952; 54520</t>
+          <t>30941; 55088</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>16899; 37076</t>
+          <t>16451; 35655</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>18711; 38952</t>
+          <t>18351; 37433</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7634; 23470</t>
+          <t>7750; 23551</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>17504; 31921</t>
+          <t>17860; 32495</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>53480; 83741</t>
+          <t>54659; 85699</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>49680; 79101</t>
+          <t>48209; 79476</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>49533; 83399</t>
+          <t>48968; 82548</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>52539; 80209</t>
+          <t>53330; 80867</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>39927; 64769</t>
+          <t>39910; 64559</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>34501; 60521</t>
+          <t>35322; 61236</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>51835; 81971</t>
+          <t>54012; 82451</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>38501; 58115</t>
+          <t>38523; 58395</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>40408; 65597</t>
+          <t>39922; 65988</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>26941; 50309</t>
+          <t>27108; 50540</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>39478; 67549</t>
+          <t>38002; 65557</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>13120; 52232</t>
+          <t>13738; 53583</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>86906; 122422</t>
+          <t>85907; 120939</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>67508; 101795</t>
+          <t>68688; 102590</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>98393; 138140</t>
+          <t>98469; 139801</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>42940; 106137</t>
+          <t>41263; 107870</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>50526; 76774</t>
+          <t>50464; 77723</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>60718; 91342</t>
+          <t>59491; 91696</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>49307; 73941</t>
+          <t>49475; 74718</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>56561; 78945</t>
+          <t>56612; 80834</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>59299; 90046</t>
+          <t>59415; 91705</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>70780; 104654</t>
+          <t>71001; 104574</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>80980; 118467</t>
+          <t>79211; 118595</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>91345; 116244</t>
+          <t>91336; 116150</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>119523; 160169</t>
+          <t>121059; 159335</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>139963; 185770</t>
+          <t>139697; 184936</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>137680; 185675</t>
+          <t>136605; 183442</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>154524; 187056</t>
+          <t>153438; 188095</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>151478; 205422</t>
+          <t>153538; 202598</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>153180; 207758</t>
+          <t>155255; 211198</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>173541; 230261</t>
+          <t>174520; 230470</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>141855; 213766</t>
+          <t>135483; 213993</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>154492; 204222</t>
+          <t>154493; 207824</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>144719; 196865</t>
+          <t>146419; 199323</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>163842; 219186</t>
+          <t>163587; 222624</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>144087; 202394</t>
+          <t>146292; 203907</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>319374; 391562</t>
+          <t>322063; 393925</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>314112; 386473</t>
+          <t>312413; 388024</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>353330; 434981</t>
+          <t>357015; 434160</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>317171; 406526</t>
+          <t>320204; 408796</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P16A10-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P16A10-Edad-trans_dic.xlsx
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,4%</t>
         </is>
       </c>
     </row>
@@ -717,12 +717,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,84</t>
+          <t>0,0; 0,83</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,07</t>
+          <t>0,0; 0,96</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,95</t>
+          <t>0,0; 1,01</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,32</t>
+          <t>0,0; 1,39</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -752,27 +752,27 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,35</t>
+          <t>0,0; 4,26</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,67</t>
+          <t>0,0; 0,63</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,77</t>
+          <t>0,0; 0,78</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,74</t>
+          <t>0,0; 0,69</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,85</t>
+          <t>0,0; 2,45</t>
         </is>
       </c>
     </row>
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,2%</t>
         </is>
       </c>
     </row>
@@ -857,17 +857,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,58</t>
+          <t>0,0; 0,65</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,66</t>
+          <t>0,15; 1,61</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,59</t>
+          <t>0,0; 1,73</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -877,42 +877,42 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,97</t>
+          <t>0,0; 1,03</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,71</t>
+          <t>0,0; 0,65</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,35; 2,09</t>
+          <t>0,35; 2,15</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,89</t>
+          <t>0,0; 1,26</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,61</t>
+          <t>0,06; 0,55</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,05</t>
+          <t>0,08; 0,89</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,34; 1,41</t>
+          <t>0,33; 1,33</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,9</t>
+          <t>0,0; 0,69</t>
         </is>
       </c>
     </row>
@@ -944,29 +944,29 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
+          <t>0,61%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>1,12%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>1,39%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>0,86%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>0,7%</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1,12%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1,39%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>0,86%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>0,7%</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
           <t>0,93%</t>
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,66%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,73</t>
+          <t>0,28; 1,59</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,63</t>
+          <t>0,27; 1,61</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,0</t>
+          <t>0,0; 0,96</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,19; 2,03</t>
+          <t>0,19; 1,82</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,49; 2,35</t>
+          <t>0,45; 2,11</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,7; 2,67</t>
+          <t>0,67; 2,58</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,74</t>
+          <t>0,42; 1,73</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,51</t>
+          <t>0,24; 1,42</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,48; 1,6</t>
+          <t>0,52; 1,54</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,64; 1,85</t>
+          <t>0,59; 1,74</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,07</t>
+          <t>0,28; 1,1</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,34</t>
+          <t>0,29; 1,26</t>
         </is>
       </c>
     </row>
@@ -1084,34 +1084,34 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
+          <t>3,94%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>3,35%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1,23%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2,26%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1,58%</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
           <t>2,91%</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>3,35%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,23%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2,26%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1,47%</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>2,91%</t>
-        </is>
-      </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
           <t>1,72%</t>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,73%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,42; 4,43</t>
+          <t>1,21; 4,4</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,08; 3,75</t>
+          <t>1,22; 3,89</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,82; 4,65</t>
+          <t>1,81; 4,59</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,23; 4,78</t>
+          <t>2,67; 5,63</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,0; 5,16</t>
+          <t>1,99; 5,32</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,53; 2,47</t>
+          <t>0,52; 2,46</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,29; 3,66</t>
+          <t>1,15; 3,74</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,84; 2,25</t>
+          <t>0,94; 2,45</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,02; 4,14</t>
+          <t>1,94; 4,18</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,1; 2,71</t>
+          <t>1,05; 2,64</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,8; 3,69</t>
+          <t>1,88; 3,82</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,29; 3,25</t>
+          <t>1,99; 3,63</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,07%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,29; 14,87</t>
+          <t>8,35; 14,6</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,16; 11,08</t>
+          <t>6,01; 11,45</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,93; 14,15</t>
+          <t>7,99; 13,95</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,52; 9,83</t>
+          <t>5,89; 9,77</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,07; 8,83</t>
+          <t>3,86; 8,68</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,11; 8,38</t>
+          <t>4,12; 8,43</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,56; 4,74</t>
+          <t>1,59; 4,74</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,28; 5,97</t>
+          <t>3,28; 6,04</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,91; 10,84</t>
+          <t>6,67; 10,58</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5,51; 9,08</t>
+          <t>5,51; 8,9</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5,02; 8,47</t>
+          <t>5,21; 8,58</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,83; 7,32</t>
+          <t>5,02; 7,55</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>10,3%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>13,64; 22,07</t>
+          <t>13,7; 21,85</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>11,48; 19,89</t>
+          <t>11,39; 19,33</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>16,16; 24,66</t>
+          <t>15,51; 24,48</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10,46; 15,86</t>
+          <t>9,98; 15,1</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>11,64; 19,24</t>
+          <t>11,79; 19,1</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7,68; 14,32</t>
+          <t>7,73; 14,27</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10,06; 17,35</t>
+          <t>10,13; 17,07</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,26; 8,81</t>
+          <t>6,52; 10,19</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>13,52; 19,03</t>
+          <t>13,39; 18,92</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>10,39; 15,53</t>
+          <t>10,4; 15,48</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>13,83; 19,63</t>
+          <t>14,07; 19,51</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>4,23; 11,05</t>
+          <t>8,84; 12,09</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,51%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>24,04; 37,03</t>
+          <t>25,29; 37,42</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>23,81; 36,7</t>
+          <t>23,97; 36,19</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>19,25; 29,07</t>
+          <t>19,42; 28,9</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>20,02; 28,59</t>
+          <t>20,69; 28,95</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>17,79; 27,46</t>
+          <t>17,76; 27,52</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,3; 26,96</t>
+          <t>18,25; 27,26</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>19,79; 29,64</t>
+          <t>20,32; 29,57</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>21,5; 27,35</t>
+          <t>21,55; 27,67</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>22,26; 29,3</t>
+          <t>21,95; 29,67</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>21,9; 29,0</t>
+          <t>22,03; 29,14</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>20,79; 27,91</t>
+          <t>21,04; 27,68</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>21,69; 26,59</t>
+          <t>22,31; 26,9</t>
         </is>
       </c>
     </row>
@@ -1644,27 +1644,27 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
+          <t>5,78%</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>5,3%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>4,8%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
           <t>5,39%</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>5,3%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>4,8%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>5,39%</t>
-        </is>
-      </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,55%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,69; 6,19</t>
+          <t>4,7; 6,18</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4,54; 6,18</t>
+          <t>4,51; 6,26</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5,14; 6,79</t>
+          <t>5,19; 6,84</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,92; 6,19</t>
+          <t>5,11; 6,52</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,57; 6,15</t>
+          <t>4,6; 6,09</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,13; 5,62</t>
+          <t>4,11; 5,54</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,62; 6,28</t>
+          <t>4,61; 6,28</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>4,0; 5,58</t>
+          <t>4,8; 5,96</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4,84; 5,92</t>
+          <t>4,8; 5,91</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4,48; 5,57</t>
+          <t>4,51; 5,54</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5,15; 6,26</t>
+          <t>5,16; 6,32</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>4,5; 5,74</t>
+          <t>5,1; 6,05</t>
         </is>
       </c>
     </row>
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2677</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2677</t>
+          <t>3081</t>
         </is>
       </c>
     </row>
@@ -2068,12 +2068,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4164</t>
+          <t>0; 4123</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 4829</t>
+          <t>0; 4347</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -2088,42 +2088,42 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4459</t>
+          <t>0; 4736</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 5660</t>
+          <t>0; 5982</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 4339</t>
+          <t>0; 4351</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 13620</t>
+          <t>0; 15430</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 6422</t>
+          <t>0; 6057</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 6833</t>
+          <t>0; 6911</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 6028</t>
+          <t>0; 5608</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 13197</t>
+          <t>0; 18893</t>
         </is>
       </c>
     </row>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2484</t>
+          <t>1964</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2484</t>
+          <t>1964</t>
         </is>
       </c>
     </row>
@@ -2276,17 +2276,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 4229</t>
+          <t>0; 4782</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1030; 11374</t>
+          <t>1031; 11053</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 9405</t>
+          <t>0; 10186</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -2296,42 +2296,42 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 6039</t>
+          <t>0; 6463</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 4344</t>
+          <t>0; 3948</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1976; 11754</t>
+          <t>1952; 12105</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 9680</t>
+          <t>0; 6333</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>869; 8255</t>
+          <t>873; 7509</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1870; 13573</t>
+          <t>1033; 11586</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3884; 16310</t>
+          <t>3791; 15376</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0; 8392</t>
+          <t>0; 6703</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3762</t>
+          <t>3797</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3785</t>
+          <t>4369</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>7547</t>
+          <t>8166</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1814; 11015</t>
+          <t>1780; 10109</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1927; 11078</t>
+          <t>1853; 10981</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 6678</t>
+          <t>0; 6408</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1033; 10876</t>
+          <t>1154; 11307</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3371; 16202</t>
+          <t>3113; 14567</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4939; 18959</t>
+          <t>4717; 18312</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1932; 11479</t>
+          <t>2796; 11450</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1453; 8190</t>
+          <t>1486; 8809</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>6410; 21182</t>
+          <t>6858; 20421</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8893; 25694</t>
+          <t>8126; 24191</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3717; 14284</t>
+          <t>3729; 14643</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3203; 14491</t>
+          <t>3575; 15642</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>25858</t>
+          <t>27616</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>10470</t>
+          <t>11668</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>36327</t>
+          <t>39284</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7352; 22980</t>
+          <t>6279; 22836</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6611; 23018</t>
+          <t>7473; 23920</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>11735; 30021</t>
+          <t>11687; 29621</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10934; 42456</t>
+          <t>18736; 39467</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>10295; 26581</t>
+          <t>10286; 27430</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3230; 15161</t>
+          <t>3219; 15086</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8345; 23733</t>
+          <t>7464; 24247</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5991; 16073</t>
+          <t>6928; 18047</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>20926; 42851</t>
+          <t>20058; 43271</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>13499; 33311</t>
+          <t>12862; 32438</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>23369; 47818</t>
+          <t>24339; 49501</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>20627; 51951</t>
+          <t>28603; 52142</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>41995</t>
+          <t>46170</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>24012</t>
+          <t>27604</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>66007</t>
+          <t>73774</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>32053; 57520</t>
+          <t>32292; 56448</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>26395; 47464</t>
+          <t>25761; 49057</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>37880; 67648</t>
+          <t>38204; 66680</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>30941; 55088</t>
+          <t>35814; 59443</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>16451; 35655</t>
+          <t>15603; 35060</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>18351; 37433</t>
+          <t>18418; 37645</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7750; 23551</t>
+          <t>7877; 23549</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>17860; 32495</t>
+          <t>19917; 36675</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>54659; 85699</t>
+          <t>52756; 83645</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>48209; 79476</t>
+          <t>48222; 77906</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>48968; 82548</t>
+          <t>50746; 83629</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>53330; 80867</t>
+          <t>61007; 91799</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>47604</t>
+          <t>50801</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>32660</t>
+          <t>36381</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>80264</t>
+          <t>87181</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>39910; 64559</t>
+          <t>40086; 63942</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>35322; 61236</t>
+          <t>35056; 59508</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>54012; 82451</t>
+          <t>51847; 81852</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>38523; 58395</t>
+          <t>40629; 61470</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>39922; 65988</t>
+          <t>40416; 65485</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>27108; 50540</t>
+          <t>27301; 50363</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>38002; 65557</t>
+          <t>38271; 64484</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>13738; 53583</t>
+          <t>28653; 44737</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>85907; 120939</t>
+          <t>85090; 120257</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>68688; 102590</t>
+          <t>68718; 102290</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>98469; 139801</t>
+          <t>100193; 138920</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>41263; 107870</t>
+          <t>74841; 102307</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>67334</t>
+          <t>75850</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>103443</t>
+          <t>113779</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>170777</t>
+          <t>189629</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>50464; 77723</t>
+          <t>53081; 78544</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>59491; 91696</t>
+          <t>59895; 90414</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>49475; 74718</t>
+          <t>49921; 74260</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>56612; 80834</t>
+          <t>64181; 89792</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>59415; 91705</t>
+          <t>59312; 91889</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>71001; 104574</t>
+          <t>70803; 105740</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>79211; 118595</t>
+          <t>81299; 118333</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>91336; 116150</t>
+          <t>99870; 128238</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>121059; 159335</t>
+          <t>119387; 161323</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>139697; 184936</t>
+          <t>140529; 185864</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>136605; 183442</t>
+          <t>138276; 181928</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>153438; 188095</t>
+          <t>172566; 208098</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>186554</t>
+          <t>204233</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>179530</t>
+          <t>198846</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>366084</t>
+          <t>403079</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>153538; 202598</t>
+          <t>153862; 202443</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>155255; 211198</t>
+          <t>154266; 214229</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>174520; 230470</t>
+          <t>176028; 232086</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>135483; 213993</t>
+          <t>180299; 230228</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>154493; 207824</t>
+          <t>155486; 205837</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>146419; 199323</t>
+          <t>145695; 196463</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>163587; 222624</t>
+          <t>163437; 222554</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>146292; 203907</t>
+          <t>179190; 222350</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>322063; 393925</t>
+          <t>319303; 393067</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>312413; 388024</t>
+          <t>314378; 386052</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>357015; 434160</t>
+          <t>358205; 438331</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>320204; 408796</t>
+          <t>370759; 439152</t>
         </is>
       </c>
     </row>
